--- a/GATEWAY/A1#111BCSSRL00000/BCS/PriamoAP/1.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111BCSSRL00000/BCS/PriamoAP/1.0/report-checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\VM-FS01\Shares\Rep-Software\A-FSE-2\Nazionale\Test Case\0 AAA VALIDAZIONE\12 - Referto Anatomia Patologica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694FB7C8-9873-4D25-8421-BDECD9E9065D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FEDB2A-846C-44BD-8694-5D8FC3405503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="658">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -2461,9 +2461,6 @@
     <t>8dc02f6dacaaa208089afc38c50f9d0f</t>
   </si>
   <si>
-    <t>2.16.840.1.113883.2.9.2.691066.4.4.a13937a39d74488d0620b7481eb8cd863d0582967d54feca52b70784a2e0452b.9265fc8dca^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>bb8604cf1a99ee187bb97c3d35704fd4</t>
   </si>
   <si>
@@ -2483,6 +2480,21 @@
   </si>
   <si>
     <t>B.C.S. Biomedical Computering Systems s.r.l.</t>
+  </si>
+  <si>
+    <t>e5653b89ad4eaac7ae3766bf73f29e0e</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.691066.4.4.00658ef6ef77558d6aff82e96980a50e4329489b4fbd613480c0239119550efc.6fb60eaa35^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.691066.4.4.7930022217b53e85f479d572ea11701ac32b5126e294dd94bc29852c8c17ad32.55f83c2f37^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>427fd844bc203de534411e99dd6b8c34</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.691066.4.4.aac8756286ad40470ee6e80e0459ab1a0b7fa17d383cd70f4ff9c7be5c5e35dd.e1d1df8513^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -4698,7 +4710,7 @@
       </c>
       <c r="B2" s="64"/>
       <c r="C2" s="65" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D2" s="64"/>
       <c r="F2" s="6"/>
@@ -10083,10 +10095,10 @@
         <v>46113.702430555553</v>
       </c>
       <c r="H148" s="31" t="s">
+        <v>650</v>
+      </c>
+      <c r="I148" s="36" t="s">
         <v>651</v>
-      </c>
-      <c r="I148" s="36" t="s">
-        <v>652</v>
       </c>
       <c r="J148" s="32" t="s">
         <v>75</v>
@@ -10123,24 +10135,44 @@
       <c r="E149" s="37" t="s">
         <v>313</v>
       </c>
-      <c r="F149" s="31"/>
-      <c r="G149" s="31"/>
-      <c r="H149" s="31"/>
-      <c r="I149" s="36"/>
+      <c r="F149" s="31">
+        <v>46125</v>
+      </c>
+      <c r="G149" s="31">
+        <v>46125.506539351853</v>
+      </c>
+      <c r="H149" s="31" t="s">
+        <v>653</v>
+      </c>
+      <c r="I149" s="36" t="s">
+        <v>654</v>
+      </c>
       <c r="J149" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="K149" s="32"/>
+      <c r="L149" s="32"/>
+      <c r="M149" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="N149" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="O149" s="32" t="s">
+        <v>634</v>
+      </c>
+      <c r="P149" s="32" t="s">
         <v>541</v>
       </c>
-      <c r="K149" s="32" t="s">
-        <v>499</v>
-      </c>
-      <c r="L149" s="32"/>
-      <c r="M149" s="32"/>
-      <c r="N149" s="32"/>
-      <c r="O149" s="32"/>
-      <c r="P149" s="32"/>
-      <c r="Q149" s="32"/>
-      <c r="R149" s="32"/>
-      <c r="S149" s="32"/>
+      <c r="Q149" s="32" t="s">
+        <v>541</v>
+      </c>
+      <c r="R149" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="S149" s="32" t="s">
+        <v>635</v>
+      </c>
       <c r="T149" s="32"/>
       <c r="U149" s="33"/>
       <c r="V149" s="34"/>
@@ -10212,10 +10244,10 @@
         <v>46112.706956018519</v>
       </c>
       <c r="H151" s="31" t="s">
+        <v>646</v>
+      </c>
+      <c r="I151" s="36" t="s">
         <v>647</v>
-      </c>
-      <c r="I151" s="36" t="s">
-        <v>648</v>
       </c>
       <c r="J151" s="32" t="s">
         <v>75</v>
@@ -10273,10 +10305,10 @@
         <v>46112.709606481483</v>
       </c>
       <c r="H152" s="31" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="I152" s="36" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="J152" s="32" t="s">
         <v>75</v>
@@ -10347,7 +10379,7 @@
         <v>75</v>
       </c>
       <c r="O153" s="32" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="P153" s="32" t="s">
         <v>541</v>
@@ -11301,24 +11333,44 @@
       <c r="E175" s="37" t="s">
         <v>363</v>
       </c>
-      <c r="F175" s="31"/>
-      <c r="G175" s="31"/>
-      <c r="H175" s="31"/>
-      <c r="I175" s="36"/>
+      <c r="F175" s="31">
+        <v>46132</v>
+      </c>
+      <c r="G175" s="31">
+        <v>46132.455057870371</v>
+      </c>
+      <c r="H175" s="31" t="s">
+        <v>656</v>
+      </c>
+      <c r="I175" s="36" t="s">
+        <v>657</v>
+      </c>
       <c r="J175" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="K175" s="32"/>
+      <c r="L175" s="32"/>
+      <c r="M175" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="N175" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="O175" s="32" t="s">
+        <v>634</v>
+      </c>
+      <c r="P175" s="32" t="s">
         <v>541</v>
       </c>
-      <c r="K175" s="32" t="s">
-        <v>499</v>
-      </c>
-      <c r="L175" s="32"/>
-      <c r="M175" s="32"/>
-      <c r="N175" s="32"/>
-      <c r="O175" s="32"/>
-      <c r="P175" s="32"/>
-      <c r="Q175" s="32"/>
-      <c r="R175" s="32"/>
-      <c r="S175" s="32"/>
+      <c r="Q175" s="32" t="s">
+        <v>541</v>
+      </c>
+      <c r="R175" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="S175" s="32" t="s">
+        <v>635</v>
+      </c>
       <c r="T175" s="32"/>
       <c r="U175" s="33"/>
       <c r="V175" s="34"/>
@@ -11685,7 +11737,7 @@
         <v>645</v>
       </c>
       <c r="I185" s="36" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="J185" s="32" t="s">
         <v>75</v>
@@ -19959,15 +20011,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20235,27 +20284,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -20280,9 +20323,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
